--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T15:14:29+00:00</t>
+    <t>2026-02-13T19:47:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the Step Count Observation, similar to the Observation Social History - Alcohol Use from the IPS.</t>
+    <t>This FHIR profile is defining the Step Count Observation, similar to the Observation Social History - Alcohol Use from the IPS. The step count option only allowes values inbetween 0 and 300 000.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation</t>
+    <t>https://fhir.hl7.at/prenudge/appdata/r4/StructureDefinition/at-prenudge-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 300 000. {valueInteger &gt;= 0 and valueInteger &lt;= 300000}</t>
   </si>
   <si>
     <t>Event</t>
@@ -660,6 +660,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="41950-7"/&gt;
+    &lt;display value="Number of steps in 24 hour Measured"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -867,8 +868,8 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+    <t xml:space="preserve">integer
+</t>
   </si>
   <si>
     <t>Actual result</t>
@@ -887,7 +888,7 @@
 </t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -906,14 +907,10 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
+    <t>Observation.value[x]:valueInteger</t>
+  </si>
+  <si>
+    <t>valueInteger</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1056,10 +1053,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>https://fhir.hl7.at/prenudge/appdata/r4/ValueSet/at-prenudge-observation-valueset-method-manual-automated</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1406,6 +1400,10 @@
   </si>
   <si>
     <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
     <t>Actual component result</t>
@@ -1754,7 +1752,7 @@
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1777,7 +1775,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -4468,7 +4466,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
@@ -4590,7 +4588,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -4605,7 +4603,7 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>273</v>
@@ -4701,10 +4699,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4730,16 +4728,16 @@
         <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4764,14 +4762,14 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4788,7 +4786,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4797,7 +4795,7 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>105</v>
@@ -4812,7 +4810,7 @@
         <v>136</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>21</v>
@@ -4823,14 +4821,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4852,16 +4850,16 @@
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4886,14 +4884,14 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4910,7 +4908,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4928,27 +4926,27 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4971,19 +4969,19 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5032,7 +5030,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5053,10 +5051,10 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -5067,10 +5065,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5096,13 +5094,13 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5131,11 +5129,11 @@
         <v>207</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5152,7 +5150,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5170,27 +5168,27 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5198,7 +5196,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5216,16 +5214,16 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5250,13 +5248,11 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5274,7 +5270,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5295,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5309,10 +5305,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5335,16 +5331,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5394,7 +5390,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5412,27 +5408,27 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5455,16 +5451,16 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5514,7 +5510,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5532,27 +5528,27 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5575,19 +5571,19 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5636,7 +5632,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5648,19 +5644,19 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5671,10 +5667,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5697,13 +5693,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5754,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5778,7 +5774,7 @@
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5789,10 +5785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5821,7 +5817,7 @@
         <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>142</v>
@@ -5874,7 +5870,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5898,7 +5894,7 @@
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5909,14 +5905,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5938,10 +5934,10 @@
         <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>142</v>
@@ -5996,7 +5992,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6031,10 +6027,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6057,13 +6053,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6114,7 +6110,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6123,7 +6119,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6135,10 +6131,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6149,10 +6145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6175,13 +6171,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6232,7 +6228,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6241,7 +6237,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6253,10 +6249,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6267,10 +6263,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6296,16 +6292,16 @@
         <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6333,10 +6329,10 @@
         <v>117</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6354,7 +6350,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6372,13 +6368,13 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6389,10 +6385,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6418,16 +6414,16 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6455,10 +6451,10 @@
         <v>207</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6476,7 +6472,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6494,13 +6490,13 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6511,10 +6507,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6537,17 +6533,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6596,7 +6592,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6620,7 +6616,7 @@
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6631,10 +6627,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6657,13 +6653,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6714,7 +6710,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6735,10 +6731,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6749,10 +6745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6775,16 +6771,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6834,7 +6830,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6855,10 +6851,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6869,10 +6865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6895,16 +6891,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6954,7 +6950,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6975,10 +6971,10 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6989,10 +6985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7015,19 +7011,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7076,7 +7072,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7097,10 +7093,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7111,10 +7107,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7137,13 +7133,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7194,7 +7190,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7218,7 +7214,7 @@
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7229,10 +7225,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7261,7 +7257,7 @@
         <v>140</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
@@ -7314,7 +7310,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7338,7 +7334,7 @@
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7349,14 +7345,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7378,10 +7374,10 @@
         <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>142</v>
@@ -7436,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7471,10 +7467,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7500,13 +7496,13 @@
         <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>205</v>
@@ -7558,7 +7554,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>93</v>
@@ -7576,7 +7572,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>212</v>
@@ -7593,10 +7589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7619,16 +7615,16 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>272</v>
+        <v>441</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>276</v>
@@ -7680,7 +7676,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7698,7 +7694,7 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>281</v>
@@ -7715,10 +7711,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7744,16 +7740,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7778,14 +7774,14 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7802,7 +7798,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7811,7 +7807,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7826,7 +7822,7 @@
         <v>136</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -7837,14 +7833,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7866,16 +7862,16 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7900,14 +7896,14 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7924,7 +7920,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7942,27 +7938,27 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7988,16 +7984,16 @@
         <v>21</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8046,7 +8042,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8067,10 +8063,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T19:47:50+00:00</t>
+    <t>2026-02-22T11:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -488,7 +491,7 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for observation</t>
+    <t>Business Identifier for observation, at least one is assigned by the data provider</t>
   </si>
   <si>
     <t>A unique identifier assigned to this observation.</t>
@@ -507,6 +510,206 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Observation.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value, if no other information is given, use your website url</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Observation.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Observation.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
     <t>Observation.basedOn</t>
@@ -582,9 +785,6 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
@@ -607,10 +807,6 @@
   </si>
   <si>
     <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of  type of observation</t>
@@ -929,9 +1125,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -989,7 +1182,7 @@
 </t>
   </si>
   <si>
-    <t>Comments about the observation</t>
+    <t>Comments about the observation including patient comments have to be possible</t>
   </si>
   <si>
     <t>Comments about the observation or the results.</t>
@@ -1150,29 +1343,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1356,7 +1527,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>Component results</t>
+    <t>Component results are not allowed as groupings for values will be handeled case by case; create only flat observations</t>
   </si>
   <si>
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
@@ -1566,6 +1737,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1747,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -1769,16 +1955,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="88.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1921,7 +2107,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2041,7 +2227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2161,7 +2347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -2279,7 +2465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -2399,7 +2585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -2519,7 +2705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2639,7 +2825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -2759,7 +2945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -2879,7 +3065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3001,7 +3187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3014,7 +3200,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>82</v>
@@ -3121,7 +3307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -3130,14 +3316,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -3146,21 +3332,19 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3208,49 +3392,49 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3266,19 +3450,19 @@
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3316,19 +3500,19 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3340,19 +3524,19 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>21</v>
@@ -3361,12 +3545,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3374,7 +3558,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3392,16 +3576,16 @@
         <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3426,13 +3610,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3450,10 +3634,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3465,30 +3649,30 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3499,7 +3683,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3508,22 +3692,22 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3548,13 +3732,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3578,7 +3762,7 @@
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3593,28 +3777,28 @@
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3633,19 +3817,19 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3655,10 +3839,10 @@
         <v>21</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>21</v>
@@ -3670,13 +3854,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3694,10 +3878,10 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>93</v>
@@ -3709,30 +3893,30 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3740,7 +3924,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>93</v>
@@ -3755,20 +3939,18 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3780,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -3816,7 +3998,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3831,30 +4013,30 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3865,7 +4047,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3877,17 +4059,15 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3936,13 +4116,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -3957,28 +4137,28 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3997,20 +4177,18 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4058,7 +4236,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4073,41 +4251,41 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4119,19 +4297,17 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4180,13 +4356,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4195,41 +4371,41 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4241,16 +4417,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4300,13 +4476,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4315,30 +4491,30 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4346,32 +4522,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>263</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4396,13 +4574,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4420,13 +4598,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4435,30 +4613,30 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4466,10 +4644,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4478,22 +4656,22 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4518,38 +4696,40 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>105</v>
@@ -4558,33 +4738,31 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4603,19 +4781,19 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4625,7 +4803,7 @@
         <v>21</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>21</v>
@@ -4640,13 +4818,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4664,45 +4842,45 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4722,22 +4900,22 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4762,13 +4940,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4786,7 +4964,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4795,40 +4973,40 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>136</v>
+        <v>286</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4844,23 +5022,21 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>290</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4884,13 +5060,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4908,7 +5084,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4926,38 +5102,38 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4966,22 +5142,22 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5030,13 +5206,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -5045,34 +5221,34 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5088,21 +5264,23 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>308</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5126,13 +5304,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5150,7 +5328,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5165,30 +5343,30 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5196,7 +5374,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5208,23 +5386,21 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5248,11 +5424,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5270,7 +5448,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5291,24 +5469,24 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5319,7 +5497,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5328,21 +5506,21 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5390,13 +5568,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5405,30 +5583,30 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5436,7 +5614,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -5448,21 +5626,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5498,19 +5678,17 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5519,7 +5697,7 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
@@ -5528,38 +5706,40 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5568,22 +5748,22 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5632,45 +5812,45 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5693,16 +5873,20 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>362</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5726,13 +5910,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5750,7 +5934,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5759,10 +5943,10 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5771,10 +5955,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5783,16 +5967,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5811,18 +5995,20 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5846,13 +6032,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5870,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5882,25 +6068,25 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35">
@@ -5912,7 +6098,7 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5922,16 +6108,16 @@
         <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>372</v>
@@ -5940,10 +6126,10 @@
         <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>142</v>
+        <v>374</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>148</v>
+        <v>375</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5992,7 +6178,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6004,7 +6190,7 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
@@ -6013,10 +6199,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6025,12 +6211,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6053,15 +6239,17 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>376</v>
+        <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6086,13 +6274,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6110,7 +6298,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6119,7 +6307,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6128,27 +6316,27 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6156,7 +6344,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
@@ -6171,16 +6359,20 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6204,13 +6396,11 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6228,7 +6418,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6237,7 +6427,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6249,10 +6439,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6261,12 +6451,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6289,20 +6479,18 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>397</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6326,13 +6514,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6350,7 +6538,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6368,27 +6556,27 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>306</v>
+        <v>403</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6399,7 +6587,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6411,20 +6599,18 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>406</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6448,13 +6634,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6472,13 +6658,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6490,27 +6676,27 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>306</v>
+        <v>412</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6521,7 +6707,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6533,17 +6719,19 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6592,19 +6780,19 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>420</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6613,10 +6801,10 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6625,12 +6813,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6653,13 +6841,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>362</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>161</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>162</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6710,7 +6898,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6722,7 +6910,7 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6731,10 +6919,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>164</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6743,16 +6931,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6768,19 +6956,19 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>414</v>
+        <v>140</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>415</v>
+        <v>166</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>416</v>
+        <v>142</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6830,7 +7018,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>170</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6842,7 +7030,7 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
@@ -6851,10 +7039,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>418</v>
+        <v>164</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6863,16 +7051,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6885,24 +7073,26 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>420</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6950,7 +7140,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6962,7 +7152,7 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -6971,10 +7161,10 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>136</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6983,12 +7173,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6999,7 +7189,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7008,23 +7198,19 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>431</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7072,16 +7258,16 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7093,10 +7279,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7105,12 +7291,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7133,13 +7319,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>439</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7190,7 +7376,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7199,10 +7385,10 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7211,10 +7397,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>440</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7223,23 +7409,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7251,18 +7437,20 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>140</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7286,13 +7474,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7310,31 +7498,31 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7343,16 +7531,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7365,25 +7553,25 @@
         <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>142</v>
+        <v>453</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>148</v>
+        <v>454</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7408,13 +7596,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7432,7 +7620,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7444,19 +7632,19 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7465,12 +7653,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7478,7 +7666,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -7490,22 +7678,20 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>458</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>205</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7530,13 +7716,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7554,10 +7740,10 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>93</v>
@@ -7572,27 +7758,27 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>213</v>
+        <v>462</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7612,23 +7798,19 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>441</v>
+        <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7676,7 +7858,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7694,27 +7876,27 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>435</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>282</v>
+        <v>466</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7725,7 +7907,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7734,23 +7916,21 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>468</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7774,13 +7954,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7798,16 +7978,16 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7819,10 +7999,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>136</v>
+        <v>472</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>295</v>
+        <v>473</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -7831,16 +8011,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7856,23 +8036,21 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>475</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>298</v>
+        <v>476</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>299</v>
+        <v>477</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7896,13 +8074,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7920,7 +8098,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7938,27 +8116,27 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>305</v>
+        <v>472</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>306</v>
+        <v>479</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7969,7 +8147,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7978,22 +8156,22 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>21</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>356</v>
+        <v>483</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>357</v>
+        <v>484</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8042,7 +8220,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8063,19 +8241,1007 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP52" t="s" s="2">
+      <c r="M59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP60">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI59">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T07:03:20+00:00</t>
+    <t>2026-02-26T10:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 300 000. {valueInteger &gt;= 0 and valueInteger &lt;= 300000}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 150 000. {valueInteger &gt;= 0 and valueInteger &lt;= 150000}</t>
   </si>
   <si>
     <t>Event</t>
@@ -617,7 +617,7 @@
     <t>Observation.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value, if no other information is given, use your website url</t>
+    <t>The namespace for the identifier value, if no other specifications are given, use your website url</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:01:13+00:00</t>
+    <t>2026-02-28T09:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the Step Count Observation, similar to the Observation Social History - Alcohol Use from the IPS. The step count option only allowes values inbetween 0 and 300 000.</t>
+    <t>This FHIR profile is defining the Step Count Observation. The step count only allows values inbetween 0 and 150,000 steps per 24 hours.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 150 000. {valueInteger &gt;= 0 and valueInteger &lt;= 150000}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 150,000. {value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 150000}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1064,7 +1064,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">integer
+    <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
@@ -1078,13 +1078,6 @@
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1103,10 +1096,138 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueInteger</t>
-  </si>
-  <si>
-    <t>valueInteger</t>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>Observation.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>{steps}/d</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>http://unitsofmeasure.org</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1246,7 +1367,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/prenudge/appdata/r4/ValueSet/at-prenudge-observation-valueset-method-manual-automated</t>
+    <t>https://fhir.hl7.at/prenudge/appdata/r4/ValueSet/prenudge-observation-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1527,7 +1648,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>Component results are not allowed as groupings for values will be handeled case by case; create only flat observations</t>
+    <t>Components should only be used when multiple values are inseparably connected to a single measurement (e.g., score domains).</t>
   </si>
   <si>
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
@@ -1933,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP60"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -1961,7 +2082,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.65625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5601,7 +5722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>334</v>
       </c>
@@ -5620,7 +5741,7 @@
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5678,14 +5799,16 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>334</v>
@@ -5697,7 +5820,7 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
@@ -5706,37 +5829,35 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -5748,23 +5869,19 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>335</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5812,7 +5929,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5821,47 +5938,47 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>345</v>
+        <v>164</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5873,20 +5990,18 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>351</v>
+        <v>166</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5910,43 +6025,43 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>349</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5955,10 +6070,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5967,47 +6082,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>348</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6032,13 +6147,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6056,13 +6171,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6074,27 +6189,27 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6105,36 +6220,36 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>371</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q35" s="2"/>
+      <c r="Q35" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="R35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6154,13 +6269,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6178,13 +6293,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6199,10 +6314,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6213,10 +6328,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6236,21 +6351,21 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -6259,7 +6374,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6274,13 +6389,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6298,7 +6413,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6316,27 +6431,27 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6344,7 +6459,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
@@ -6356,22 +6471,20 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6381,7 +6494,7 @@
         <v>21</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>21</v>
@@ -6396,11 +6509,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6418,7 +6533,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6427,7 +6542,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6439,10 +6554,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6453,10 +6568,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6476,21 +6591,23 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>397</v>
+        <v>113</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6499,7 +6616,7 @@
         <v>21</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>21</v>
@@ -6538,7 +6655,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6556,27 +6673,27 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6599,18 +6716,20 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>406</v>
+        <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6634,13 +6753,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6658,7 +6777,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6667,7 +6786,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6676,31 +6795,31 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>411</v>
+        <v>136</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6719,19 +6838,19 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>415</v>
+        <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6756,13 +6875,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6780,7 +6899,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6792,33 +6911,33 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6829,10 +6948,10 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6841,16 +6960,20 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>160</v>
+        <v>411</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>161</v>
+        <v>412</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6898,19 +7021,19 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>163</v>
+        <v>410</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6919,10 +7042,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>164</v>
+        <v>417</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6933,21 +7056,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6959,16 +7082,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>166</v>
+        <v>420</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>142</v>
+        <v>421</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6994,13 +7117,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7018,80 +7141,80 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>170</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>164</v>
+        <v>426</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>142</v>
+        <v>431</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>148</v>
+        <v>432</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7116,13 +7239,11 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>433</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7140,19 +7261,19 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -7161,10 +7282,10 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>136</v>
+        <v>435</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7175,10 +7296,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7201,15 +7322,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7258,7 +7381,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7267,7 +7390,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7276,27 +7399,27 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7319,15 +7442,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7376,7 +7501,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7385,7 +7510,7 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7394,27 +7519,27 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>21</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7425,7 +7550,7 @@
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7437,19 +7562,19 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>455</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7474,13 +7599,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7498,31 +7623,31 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>460</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>462</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7533,10 +7658,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7547,7 +7672,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7559,20 +7684,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>161</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7596,13 +7717,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>456</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7620,31 +7741,31 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>450</v>
+        <v>163</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>368</v>
+        <v>164</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7655,21 +7776,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7681,18 +7802,18 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>458</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>459</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7740,19 +7861,19 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>170</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7764,7 +7885,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>462</v>
+        <v>164</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7775,42 +7896,46 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7858,19 +7983,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7879,10 +8004,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>466</v>
+        <v>136</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7893,10 +8018,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7907,7 +8032,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7916,20 +8041,18 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7978,16 +8101,16 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7999,10 +8122,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8013,10 +8136,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8027,7 +8150,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8036,20 +8159,18 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8098,16 +8219,16 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI51" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8119,10 +8240,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8133,10 +8254,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8147,7 +8268,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8156,22 +8277,22 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>182</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8196,13 +8317,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>486</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8220,13 +8341,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8238,13 +8359,13 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>21</v>
+        <v>488</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>486</v>
+        <v>408</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8255,10 +8376,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8269,7 +8390,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8281,16 +8402,20 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>161</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8314,13 +8439,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8338,31 +8463,31 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>163</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>488</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>164</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8373,21 +8498,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8399,18 +8524,18 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>498</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>140</v>
+        <v>499</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8458,19 +8583,19 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>170</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8482,7 +8607,7 @@
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>164</v>
+        <v>502</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>21</v>
@@ -8493,46 +8618,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>427</v>
+        <v>504</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8580,19 +8701,19 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8601,10 +8722,10 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>506</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8615,10 +8736,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8626,10 +8747,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8641,20 +8762,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>182</v>
+        <v>508</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8678,13 +8797,13 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8702,13 +8821,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8720,16 +8839,16 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>275</v>
+        <v>512</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>276</v>
+        <v>513</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>21</v>
@@ -8737,10 +8856,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8751,7 +8870,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8763,20 +8882,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>337</v>
+        <v>517</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8824,13 +8941,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8842,27 +8959,27 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>344</v>
+        <v>512</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>345</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8873,7 +8990,7 @@
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8882,22 +8999,22 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>182</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>353</v>
+        <v>524</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8922,13 +9039,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -8946,16 +9063,16 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -8967,10 +9084,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>136</v>
+        <v>525</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>357</v>
+        <v>526</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8981,21 +9098,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9007,20 +9124,16 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>360</v>
+        <v>161</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9044,13 +9157,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9068,49 +9181,49 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>163</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>368</v>
+        <v>164</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9129,20 +9242,18 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>506</v>
+        <v>140</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>507</v>
+        <v>166</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9190,7 +9301,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>505</v>
+        <v>170</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9202,29 +9313,761 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP60">
+  <autoFilter ref="A1:AP66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9234,7 +10077,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$67</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2609" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,8 +980,8 @@
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>Clinically relevant time/time-period for observation</t>
@@ -996,6 +996,13 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -1006,6 +1013,15 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t>The mandatory clinically relevant time for observation</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1411,7 +1427,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>(Measurement) Devices should be documented when used</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -2054,12 +2070,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AP67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.40234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -5373,7 +5389,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
@@ -5437,16 +5453,14 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>306</v>
@@ -5464,19 +5478,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>21</v>
@@ -5484,18 +5498,20 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5510,18 +5526,20 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5569,7 +5587,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5584,19 +5602,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>21</v>
@@ -5604,10 +5622,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5618,7 +5636,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5630,18 +5648,18 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5689,13 +5707,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5704,30 +5722,30 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5735,13 +5753,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5750,19 +5768,17 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5811,45 +5827,45 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5857,7 +5873,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -5869,19 +5885,23 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>161</v>
+        <v>341</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5929,7 +5949,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>339</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5938,47 +5958,47 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>164</v>
+        <v>348</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5990,17 +6010,15 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -6037,31 +6055,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -6082,48 +6100,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>348</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>349</v>
+        <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>350</v>
+        <v>166</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6159,31 +6175,31 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>353</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -6192,10 +6208,10 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6206,10 +6222,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6217,7 +6233,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
@@ -6226,74 +6242,74 @@
         <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>113</v>
+        <v>353</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6314,10 +6330,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6328,10 +6344,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6348,33 +6364,35 @@
         <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q36" s="2"/>
+      <c r="Q36" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="R36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6389,13 +6407,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6413,7 +6431,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6434,10 +6452,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6448,10 +6466,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6474,17 +6492,17 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6494,7 +6512,7 @@
         <v>21</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>21</v>
@@ -6533,7 +6551,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6542,7 +6560,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6554,10 +6572,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6568,10 +6586,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6594,19 +6612,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6616,7 +6632,7 @@
         <v>21</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>21</v>
@@ -6655,7 +6671,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6664,7 +6680,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6676,10 +6692,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6690,10 +6706,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6713,22 +6729,22 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6738,7 +6754,7 @@
         <v>21</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>21</v>
@@ -6753,13 +6769,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6777,7 +6793,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6786,7 +6802,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6798,10 +6814,10 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6812,21 +6828,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6841,16 +6857,16 @@
         <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6878,10 +6894,10 @@
         <v>187</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6899,16 +6915,16 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6917,31 +6933,31 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>407</v>
+        <v>136</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6951,7 +6967,7 @@
         <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6960,19 +6976,19 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>411</v>
+        <v>182</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6997,13 +7013,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -7021,7 +7037,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7039,27 +7055,27 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>21</v>
+        <v>414</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7070,10 +7086,10 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -7082,18 +7098,20 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>416</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -7117,13 +7135,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7141,13 +7159,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -7159,27 +7177,27 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>427</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7187,7 +7205,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7205,17 +7223,15 @@
         <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7239,11 +7255,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7261,7 +7279,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7279,27 +7297,27 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7307,7 +7325,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
@@ -7322,18 +7340,20 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7357,13 +7377,11 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7381,7 +7399,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7399,27 +7417,27 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7442,16 +7460,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7501,7 +7519,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7519,27 +7537,27 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7550,10 +7568,10 @@
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7562,20 +7580,18 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7623,45 +7639,45 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>460</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7672,7 +7688,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7684,16 +7700,20 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>161</v>
+        <v>461</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7741,19 +7761,19 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>163</v>
+        <v>459</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7762,10 +7782,10 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>164</v>
+        <v>467</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7776,21 +7796,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7802,17 +7822,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7861,19 +7879,19 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7896,14 +7914,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7916,26 +7934,24 @@
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>467</v>
+        <v>140</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>468</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O49" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7983,7 +7999,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>469</v>
+        <v>170</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8007,7 +8023,7 @@
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -8025,26 +8041,26 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>471</v>
+        <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>472</v>
@@ -8052,8 +8068,12 @@
       <c r="M50" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8101,19 +8121,19 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>474</v>
+        <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
@@ -8122,10 +8142,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>136</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8136,10 +8156,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8162,13 +8182,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8219,7 +8239,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8228,7 +8248,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8240,10 +8260,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8254,10 +8274,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8280,20 +8300,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>182</v>
+        <v>476</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N52" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8317,13 +8333,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>486</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8341,7 +8357,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8350,7 +8366,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>21</v>
+        <v>479</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8359,13 +8375,13 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>408</v>
+        <v>485</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8376,10 +8392,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8390,7 +8406,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8405,16 +8421,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8439,13 +8455,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8463,13 +8479,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8481,13 +8497,13 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8498,10 +8514,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8512,7 +8528,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8524,17 +8540,19 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8559,13 +8577,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>21</v>
+        <v>501</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8583,13 +8601,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -8601,13 +8619,13 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>21</v>
+        <v>494</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>502</v>
+        <v>413</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>21</v>
@@ -8618,10 +8636,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8644,7 +8662,7 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>160</v>
+        <v>503</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>504</v>
@@ -8653,7 +8671,9 @@
         <v>505</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8701,7 +8721,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8722,10 +8742,10 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8736,10 +8756,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8750,7 +8770,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8759,10 +8779,10 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>508</v>
+        <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>509</v>
@@ -8770,9 +8790,7 @@
       <c r="M56" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N56" t="s" s="2">
-        <v>511</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8821,13 +8839,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8842,10 +8860,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8856,10 +8874,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8882,16 +8900,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8941,7 +8959,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8962,10 +8980,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8976,10 +8994,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9002,7 +9020,7 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>455</v>
+        <v>520</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>521</v>
@@ -9013,9 +9031,7 @@
       <c r="N58" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>524</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9063,7 +9079,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9084,10 +9100,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9098,10 +9114,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9112,7 +9128,7 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9121,19 +9137,23 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>161</v>
+        <v>526</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9181,19 +9201,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>163</v>
+        <v>525</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9202,10 +9222,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>21</v>
+        <v>530</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>164</v>
+        <v>531</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9216,21 +9236,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9242,17 +9262,15 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9301,19 +9319,19 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9336,14 +9354,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9356,26 +9374,24 @@
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>140</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>166</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O61" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9423,7 +9439,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>170</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9447,7 +9463,7 @@
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9458,45 +9474,45 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>532</v>
+        <v>473</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>533</v>
+        <v>142</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>268</v>
+        <v>148</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9521,13 +9537,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9545,34 +9561,34 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>534</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>21</v>
@@ -9591,7 +9607,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
@@ -9606,19 +9622,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>538</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9643,13 +9659,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9670,7 +9686,7 @@
         <v>535</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>93</v>
@@ -9688,16 +9704,16 @@
         <v>539</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>342</v>
+        <v>275</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>343</v>
+        <v>276</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -9725,22 +9741,22 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>182</v>
+        <v>541</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
+        <v>342</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>543</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9765,13 +9781,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9798,7 +9814,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -9807,38 +9823,38 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>136</v>
+        <v>347</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9853,16 +9869,16 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>401</v>
+        <v>547</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>402</v>
+        <v>548</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9890,10 +9906,10 @@
         <v>187</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9911,16 +9927,16 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -9929,31 +9945,31 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>407</v>
+        <v>136</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9972,19 +9988,19 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>546</v>
+        <v>405</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>547</v>
+        <v>406</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10009,13 +10025,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10033,7 +10049,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10051,23 +10067,145 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>462</v>
+        <v>413</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP66">
+  <autoFilter ref="A1:AP67">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10077,7 +10215,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1031,7 +1031,7 @@
 </t>
   </si>
   <si>
-    <t>Date/Time this version was made available</t>
+    <t>The mandatory date/time this version was made available</t>
   </si>
   <si>
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}stepcount-range:Step count must be inbetween 0 and 150,000. {value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 150000}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}stepcount-range:Step count must be inbetween 0 and 150,000. {value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 150000}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1249,7 +1249,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -1726,7 +1726,7 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
+    <t>Reason why no clinically or analytically meaningful component result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
@@ -6826,7 +6826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>394</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -9838,7 +9838,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>545</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-stepcount-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
